--- a/financial_advisor_forms/021_wallets_recommendation_quiz--financial_advisor_forms.xlsx
+++ b/financial_advisor_forms/021_wallets_recommendation_quiz--financial_advisor_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -801,7 +801,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>What wallet size would you like?</t>
+          <t>Wallet Size 3</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -819,12 +819,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>color_2</t>
+          <t>color_2_2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>What color would you like your wallet?</t>
+          <t>Color 2 2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -847,7 +847,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Do you want a wallet with RFID-blocking technology?</t>
+          <t>Wallet Security 3</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -870,7 +870,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Find the perfect wallet</t>
+          <t>Find Perfect Wallet 3</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -893,7 +893,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>What wallet size would you like?</t>
+          <t>Wallet 2 Size 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -916,7 +916,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Do you want a wallet with RFID-blocking technology?</t>
+          <t>Security Feature 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -962,7 +962,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Do you want any security features in your wallet?</t>
+          <t>Security 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -1077,7 +1077,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Do you want a wallet with RFID-blocking technology?</t>
+          <t>Wallet 3 Security 2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1670,7 +1670,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>color_2_choices</t>
+          <t>color_2_2_choices</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1687,7 +1687,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>color_2_choices</t>
+          <t>color_2_2_choices</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1704,7 +1704,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>color_2_choices</t>
+          <t>color_2_2_choices</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1760,12 +1760,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1777,12 +1777,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1794,12 +1794,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
